--- a/examples/02_Ta2O5_on_fused_silica_60deg.xlsx
+++ b/examples/02_Ta2O5_on_fused_silica_60deg.xlsx
@@ -3901,7 +3901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -4049,10 +4049,22 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
+          <t>Возможные дефекты</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>неоднородность по глубине (линейный градиент n), шероховатость поверхности (EMA-слой Бруггемана 50/50), поглощение (хвост ниже края: второй осциллятор Тауца–Лоренца с теми же E0, C и порогом E_t = 1.2 эВ; размер — k хвоста при 400 нм)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
           <t>Назначение</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>тестовый файл для приложения: опорный фит однородной плёнки → ИИ по остатку → окончательный фит; истинные параметры — в answer_key.xlsx</t>
         </is>

--- a/examples/02_Ta2O5_on_fused_silica_60deg.xlsx
+++ b/examples/02_Ta2O5_on_fused_silica_60deg.xlsx
@@ -3901,7 +3901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3971,100 +3971,112 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Угол падения, град</t>
+          <t>Задняя сторона подложки</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
-        <v>60</v>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>нет (зачернена / матирована / отсечена)</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Толщина (номинал), нм</t>
+          <t>Угол падения, град</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>850</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
+          <t>Толщина (номинал), нм</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
           <t>Неопределённость толщины, %</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>±6</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Диапазон длин волн, нм</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>400 – 800, шаг 2</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Спектральная полоса прибора, нм (FWHM)</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B11" s="4" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Шумовая модель</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>столбцы σΨ, σΔ — повторяемость прибора (σΔ растёт при Ψ → 0)</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Прибор</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>RCE-эллипсометр с ПЗС, все длины волн одновременно; Δ в диапазоне 0–360°; конвенция N = n − ik (Аззам–Башара)</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Возможные дефекты</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>неоднородность по глубине (линейный градиент n), шероховатость поверхности (EMA-слой Бруггемана 50/50), поглощение (хвост ниже края: второй осциллятор Тауца–Лоренца с теми же E0, C и порогом E_t = 1.2 эВ; размер — k хвоста при 400 нм)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Назначение</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>тестовый файл для приложения: опорный фит однородной плёнки → ИИ по остатку → окончательный фит; истинные параметры — в answer_key.xlsx</t>
         </is>

--- a/examples/02_Ta2O5_on_fused_silica_60deg.xlsx
+++ b/examples/02_Ta2O5_on_fused_silica_60deg.xlsx
@@ -478,16 +478,16 @@
         <v>400</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>11.2372</v>
+        <v>11.2661</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>98.60939999999999</v>
+        <v>98.94629999999999</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0.035</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.2005</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="3">
@@ -495,16 +495,16 @@
         <v>402</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>13.0603</v>
+        <v>13.0772</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>118.1829</v>
+        <v>118.3594</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>0.0347</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.173</v>
+        <v>0.1727</v>
       </c>
     </row>
     <row r="4">
@@ -512,10 +512,10 @@
         <v>404</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>14.377</v>
+        <v>14.3863</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>131.9988</v>
+        <v>132.0939</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>0.0344</v>
@@ -529,16 +529,16 @@
         <v>406</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>15.3605</v>
+        <v>15.3654</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>142.8109</v>
+        <v>142.8658</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>0.0341</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.1462</v>
+        <v>0.1461</v>
       </c>
     </row>
     <row r="6">
@@ -546,10 +546,10 @@
         <v>408</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>16.1827</v>
+        <v>16.185</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>152.1567</v>
+        <v>152.1893</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>0.0337</v>
@@ -563,10 +563,10 @@
         <v>410</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>16.6063</v>
+        <v>16.6073</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>160.4267</v>
+        <v>160.4455</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>0.0334</v>
@@ -580,10 +580,10 @@
         <v>412</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>16.9264</v>
+        <v>16.9266</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>168.3497</v>
+        <v>168.3585</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>0.0331</v>
@@ -600,7 +600,7 @@
         <v>17.0005</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>176.3011</v>
+        <v>176.3018</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>0.0328</v>
@@ -614,10 +614,10 @@
         <v>416</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>16.7801</v>
+        <v>16.7803</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>183.7458</v>
+        <v>183.739</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>0.0325</v>
@@ -631,10 +631,10 @@
         <v>418</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>16.4458</v>
+        <v>16.4467</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>191.8062</v>
+        <v>191.7918</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>0.0322</v>
@@ -648,10 +648,10 @@
         <v>420</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>15.8545</v>
+        <v>15.8565</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>199.8179</v>
+        <v>199.7942</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>0.0319</v>
@@ -665,10 +665,10 @@
         <v>422</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>15.0947</v>
+        <v>15.0983</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>208.2344</v>
+        <v>208.1983</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>0.0316</v>
@@ -682,10 +682,10 @@
         <v>424</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>14.1041</v>
+        <v>14.11</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>217.1644</v>
+        <v>217.1098</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>0.0313</v>
@@ -699,16 +699,16 @@
         <v>426</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>13.004</v>
+        <v>13.0131</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>227.4396</v>
+        <v>227.3544</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>0.0311</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.1554</v>
+        <v>0.1553</v>
       </c>
     </row>
     <row r="16">
@@ -716,16 +716,16 @@
         <v>428</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>11.7092</v>
+        <v>11.7226</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>240.4405</v>
+        <v>240.3014</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>0.0308</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.17</v>
+        <v>0.1698</v>
       </c>
     </row>
     <row r="17">
@@ -733,16 +733,16 @@
         <v>430</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>10.1931</v>
+        <v>10.2114</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>258.1279</v>
+        <v>257.8978</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>0.0305</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.1928</v>
+        <v>0.1925</v>
       </c>
     </row>
     <row r="18">
@@ -750,16 +750,16 @@
         <v>432</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>8.420299999999999</v>
+        <v>8.438599999999999</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>284.9054</v>
+        <v>284.564</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>0.0302</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0.2301</v>
+        <v>0.2296</v>
       </c>
     </row>
     <row r="19">
@@ -767,16 +767,16 @@
         <v>434</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>6.9526</v>
+        <v>6.9577</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>327.9699</v>
+        <v>327.6931</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>0.0299</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.2755</v>
+        <v>0.2753</v>
       </c>
     </row>
     <row r="20">
@@ -784,16 +784,16 @@
         <v>436</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>7.0325</v>
+        <v>7.0359</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>22.4587</v>
+        <v>22.5939</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>0.0297</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.2674</v>
+        <v>0.2673</v>
       </c>
     </row>
     <row r="21">
@@ -801,16 +801,16 @@
         <v>438</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>8.7323</v>
+        <v>8.7483</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>64.4469</v>
+        <v>64.7337</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>0.0294</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.2159</v>
+        <v>0.2155</v>
       </c>
     </row>
     <row r="22">
@@ -818,16 +818,16 @@
         <v>440</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>10.4579</v>
+        <v>10.4741</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>91.8871</v>
+        <v>92.1052</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>0.0291</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0.1792</v>
+        <v>0.1789</v>
       </c>
     </row>
     <row r="23">
@@ -835,16 +835,16 @@
         <v>442</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>11.8844</v>
+        <v>11.8959</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>109.2457</v>
+        <v>109.3833</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>0.0288</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.1575</v>
+        <v>0.1574</v>
       </c>
     </row>
     <row r="24">
@@ -852,16 +852,16 @@
         <v>444</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>12.9484</v>
+        <v>12.9559</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>122.445</v>
+        <v>122.5294</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>0.0286</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0.1437</v>
+        <v>0.1436</v>
       </c>
     </row>
     <row r="25">
@@ -869,16 +869,16 @@
         <v>446</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>13.8418</v>
+        <v>13.8466</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>132.3822</v>
+        <v>132.4359</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>0.0283</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0.1339</v>
+        <v>0.1338</v>
       </c>
     </row>
     <row r="26">
@@ -886,10 +886,10 @@
         <v>448</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>14.5668</v>
+        <v>14.5697</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>140.7294</v>
+        <v>140.7647</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>0.0281</v>
@@ -903,10 +903,10 @@
         <v>450</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>15.1724</v>
+        <v>15.1741</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>148.1708</v>
+        <v>148.1946</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>0.0278</v>
@@ -920,10 +920,10 @@
         <v>452</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>15.6462</v>
+        <v>15.6472</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>154.9607</v>
+        <v>154.9767</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>0.0275</v>
@@ -937,10 +937,10 @@
         <v>454</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>15.9577</v>
+        <v>15.9581</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>161.4056</v>
+        <v>161.4159</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>0.0273</v>
@@ -954,10 +954,10 @@
         <v>456</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>16.1493</v>
+        <v>16.1494</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>167.5328</v>
+        <v>167.5386</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>0.027</v>
@@ -974,7 +974,7 @@
         <v>16.2185</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>173.9792</v>
+        <v>173.9812</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>0.0268</v>
@@ -988,10 +988,10 @@
         <v>460</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>16.1938</v>
+        <v>16.1939</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>179.7164</v>
+        <v>179.7151</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>0.0266</v>
@@ -1005,10 +1005,10 @@
         <v>462</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>16.0287</v>
+        <v>16.0289</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>185.6109</v>
+        <v>185.6062</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>0.0263</v>
@@ -1022,10 +1022,10 @@
         <v>464</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>15.7304</v>
+        <v>15.7309</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>191.6838</v>
+        <v>191.6757</v>
       </c>
       <c r="D34" s="2" t="n">
         <v>0.0261</v>
@@ -1039,10 +1039,10 @@
         <v>466</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>15.3275</v>
+        <v>15.3283</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>197.7018</v>
+        <v>197.6899</v>
       </c>
       <c r="D35" s="2" t="n">
         <v>0.0258</v>
@@ -1056,10 +1056,10 @@
         <v>468</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>14.8325</v>
+        <v>14.8339</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>204.0003</v>
+        <v>203.9837</v>
       </c>
       <c r="D36" s="2" t="n">
         <v>0.0256</v>
@@ -1073,10 +1073,10 @@
         <v>470</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>14.2901</v>
+        <v>14.2922</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>210.6393</v>
+        <v>210.6168</v>
       </c>
       <c r="D37" s="2" t="n">
         <v>0.0254</v>
@@ -1090,10 +1090,10 @@
         <v>472</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>13.5875</v>
+        <v>13.5905</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>217.6245</v>
+        <v>217.5937</v>
       </c>
       <c r="D38" s="2" t="n">
         <v>0.0251</v>
@@ -1107,10 +1107,10 @@
         <v>474</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>12.8132</v>
+        <v>12.8173</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>225.2169</v>
+        <v>225.1743</v>
       </c>
       <c r="D39" s="2" t="n">
         <v>0.0249</v>
@@ -1124,10 +1124,10 @@
         <v>476</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>12.032</v>
+        <v>12.0376</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>234.4566</v>
+        <v>234.3964</v>
       </c>
       <c r="D40" s="2" t="n">
         <v>0.0247</v>
@@ -1141,16 +1141,16 @@
         <v>478</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>11.0365</v>
+        <v>11.0438</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>245.195</v>
+        <v>245.1084</v>
       </c>
       <c r="D41" s="2" t="n">
         <v>0.0245</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>0.1428</v>
+        <v>0.1427</v>
       </c>
     </row>
     <row r="42">
@@ -1158,16 +1158,16 @@
         <v>480</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>9.9254</v>
+        <v>9.9344</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>258.7599</v>
+        <v>258.6358</v>
       </c>
       <c r="D42" s="2" t="n">
         <v>0.0242</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>0.156</v>
+        <v>0.1559</v>
       </c>
     </row>
     <row r="43">
@@ -1175,16 +1175,16 @@
         <v>482</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>8.75</v>
+        <v>8.759499999999999</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>277.316</v>
+        <v>277.1479</v>
       </c>
       <c r="D43" s="2" t="n">
         <v>0.024</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>0.1748</v>
+        <v>0.1746</v>
       </c>
     </row>
     <row r="44">
@@ -1192,16 +1192,16 @@
         <v>484</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>7.5698</v>
+        <v>7.5764</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>302.9024</v>
+        <v>302.7147</v>
       </c>
       <c r="D44" s="2" t="n">
         <v>0.0238</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>0.1991</v>
+        <v>0.1989</v>
       </c>
     </row>
     <row r="45">
@@ -1209,16 +1209,16 @@
         <v>486</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>6.8808</v>
+        <v>6.882</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>337.3245</v>
+        <v>337.2131</v>
       </c>
       <c r="D45" s="2" t="n">
         <v>0.0236</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>0.2188</v>
+        <v>0.2187</v>
       </c>
     </row>
     <row r="46">
@@ -1226,10 +1226,10 @@
         <v>488</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>6.9829</v>
+        <v>6.9838</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>16.9228</v>
+        <v>16.9748</v>
       </c>
       <c r="D46" s="2" t="n">
         <v>0.0234</v>
@@ -1243,16 +1243,16 @@
         <v>490</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>7.9556</v>
+        <v>7.9616</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>49.8856</v>
+        <v>50.0307</v>
       </c>
       <c r="D47" s="2" t="n">
         <v>0.0232</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>0.1857</v>
+        <v>0.1856</v>
       </c>
     </row>
     <row r="48">
@@ -1260,16 +1260,16 @@
         <v>492</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>9.1637</v>
+        <v>9.1721</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>74.78749999999999</v>
+        <v>74.9327</v>
       </c>
       <c r="D48" s="2" t="n">
         <v>0.023</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>0.1603</v>
+        <v>0.1601</v>
       </c>
     </row>
     <row r="49">
@@ -1277,16 +1277,16 @@
         <v>494</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>10.3024</v>
+        <v>10.3102</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>92.5908</v>
+        <v>92.7039</v>
       </c>
       <c r="D49" s="2" t="n">
         <v>0.0228</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>0.1421</v>
+        <v>0.142</v>
       </c>
     </row>
     <row r="50">
@@ -1294,10 +1294,10 @@
         <v>496</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>11.315</v>
+        <v>11.3211</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>105.9698</v>
+        <v>106.0506</v>
       </c>
       <c r="D50" s="2" t="n">
         <v>0.0226</v>
@@ -1311,16 +1311,16 @@
         <v>498</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>12.0805</v>
+        <v>12.0849</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>116.3709</v>
+        <v>116.4276</v>
       </c>
       <c r="D51" s="2" t="n">
         <v>0.0224</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>0.1203</v>
+        <v>0.1202</v>
       </c>
     </row>
     <row r="52">
@@ -1328,10 +1328,10 @@
         <v>500</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>12.7718</v>
+        <v>12.775</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>125.0816</v>
+        <v>125.1217</v>
       </c>
       <c r="D52" s="2" t="n">
         <v>0.0222</v>
@@ -1345,10 +1345,10 @@
         <v>502</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>13.3896</v>
+        <v>13.3919</v>
       </c>
       <c r="C53" s="2" t="n">
-        <v>132.3699</v>
+        <v>132.3988</v>
       </c>
       <c r="D53" s="2" t="n">
         <v>0.022</v>
@@ -1362,10 +1362,10 @@
         <v>504</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>13.8934</v>
+        <v>13.895</v>
       </c>
       <c r="C54" s="2" t="n">
-        <v>138.7713</v>
+        <v>138.7925</v>
       </c>
       <c r="D54" s="2" t="n">
         <v>0.0218</v>
@@ -1379,10 +1379,10 @@
         <v>506</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>14.2791</v>
+        <v>14.2802</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>144.5197</v>
+        <v>144.5355</v>
       </c>
       <c r="D55" s="2" t="n">
         <v>0.0216</v>
@@ -1396,10 +1396,10 @@
         <v>508</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>14.6924</v>
+        <v>14.6931</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>150.0484</v>
+        <v>150.0602</v>
       </c>
       <c r="D56" s="2" t="n">
         <v>0.0215</v>
@@ -1413,10 +1413,10 @@
         <v>510</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>14.9428</v>
+        <v>14.9433</v>
       </c>
       <c r="C57" s="2" t="n">
-        <v>155.0305</v>
+        <v>155.0393</v>
       </c>
       <c r="D57" s="2" t="n">
         <v>0.0213</v>
@@ -1430,10 +1430,10 @@
         <v>512</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>15.2082</v>
+        <v>15.2085</v>
       </c>
       <c r="C58" s="2" t="n">
-        <v>159.9048</v>
+        <v>159.9111</v>
       </c>
       <c r="D58" s="2" t="n">
         <v>0.0211</v>
@@ -1447,10 +1447,10 @@
         <v>514</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>15.4001</v>
+        <v>15.4002</v>
       </c>
       <c r="C59" s="2" t="n">
-        <v>164.5833</v>
+        <v>164.5876</v>
       </c>
       <c r="D59" s="2" t="n">
         <v>0.0209</v>
@@ -1464,10 +1464,10 @@
         <v>516</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>15.4573</v>
+        <v>15.4574</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>169.2857</v>
+        <v>169.2884</v>
       </c>
       <c r="D60" s="2" t="n">
         <v>0.0207</v>
@@ -1484,7 +1484,7 @@
         <v>15.5548</v>
       </c>
       <c r="C61" s="2" t="n">
-        <v>173.8799</v>
+        <v>173.8811</v>
       </c>
       <c r="D61" s="2" t="n">
         <v>0.0206</v>
@@ -1501,7 +1501,7 @@
         <v>15.4914</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>178.2727</v>
+        <v>178.2725</v>
       </c>
       <c r="D62" s="2" t="n">
         <v>0.0204</v>
@@ -1518,7 +1518,7 @@
         <v>15.4579</v>
       </c>
       <c r="C63" s="2" t="n">
-        <v>182.8896</v>
+        <v>182.8881</v>
       </c>
       <c r="D63" s="2" t="n">
         <v>0.0202</v>
@@ -1532,10 +1532,10 @@
         <v>524</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>15.2626</v>
+        <v>15.2627</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>187.3843</v>
+        <v>187.3814</v>
       </c>
       <c r="D64" s="2" t="n">
         <v>0.0201</v>
@@ -1549,10 +1549,10 @@
         <v>526</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>15.0584</v>
+        <v>15.0586</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>191.7249</v>
+        <v>191.7206</v>
       </c>
       <c r="D65" s="2" t="n">
         <v>0.0199</v>
@@ -1566,10 +1566,10 @@
         <v>528</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>14.8527</v>
+        <v>14.8531</v>
       </c>
       <c r="C66" s="2" t="n">
-        <v>196.3397</v>
+        <v>196.334</v>
       </c>
       <c r="D66" s="2" t="n">
         <v>0.0198</v>
@@ -1583,10 +1583,10 @@
         <v>530</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>14.5438</v>
+        <v>14.5443</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>200.9034</v>
+        <v>200.8959</v>
       </c>
       <c r="D67" s="2" t="n">
         <v>0.0196</v>
@@ -1600,10 +1600,10 @@
         <v>532</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>14.1866</v>
+        <v>14.1873</v>
       </c>
       <c r="C68" s="2" t="n">
-        <v>205.663</v>
+        <v>205.6536</v>
       </c>
       <c r="D68" s="2" t="n">
         <v>0.0195</v>
@@ -1617,10 +1617,10 @@
         <v>534</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>13.823</v>
+        <v>13.824</v>
       </c>
       <c r="C69" s="2" t="n">
-        <v>210.581</v>
+        <v>210.5692</v>
       </c>
       <c r="D69" s="2" t="n">
         <v>0.0193</v>
@@ -1634,10 +1634,10 @@
         <v>536</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>13.3724</v>
+        <v>13.3737</v>
       </c>
       <c r="C70" s="2" t="n">
-        <v>215.398</v>
+        <v>215.3834</v>
       </c>
       <c r="D70" s="2" t="n">
         <v>0.0192</v>
@@ -1651,10 +1651,10 @@
         <v>538</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>12.878</v>
+        <v>12.8796</v>
       </c>
       <c r="C71" s="2" t="n">
-        <v>221.1355</v>
+        <v>221.1171</v>
       </c>
       <c r="D71" s="2" t="n">
         <v>0.019</v>
@@ -1668,10 +1668,10 @@
         <v>540</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>12.3511</v>
+        <v>12.3531</v>
       </c>
       <c r="C72" s="2" t="n">
-        <v>227.1184</v>
+        <v>227.0952</v>
       </c>
       <c r="D72" s="2" t="n">
         <v>0.0189</v>
@@ -1685,10 +1685,10 @@
         <v>542</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>11.7696</v>
+        <v>11.7721</v>
       </c>
       <c r="C73" s="2" t="n">
-        <v>233.3701</v>
+        <v>233.3406</v>
       </c>
       <c r="D73" s="2" t="n">
         <v>0.0187</v>
@@ -1702,10 +1702,10 @@
         <v>544</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>11.1812</v>
+        <v>11.1842</v>
       </c>
       <c r="C74" s="2" t="n">
-        <v>240.886</v>
+        <v>240.8479</v>
       </c>
       <c r="D74" s="2" t="n">
         <v>0.0186</v>
@@ -1719,10 +1719,10 @@
         <v>546</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>10.543</v>
+        <v>10.5466</v>
       </c>
       <c r="C75" s="2" t="n">
-        <v>249.5207</v>
+        <v>249.4715</v>
       </c>
       <c r="D75" s="2" t="n">
         <v>0.0185</v>
@@ -1736,16 +1736,16 @@
         <v>548</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>9.8011</v>
+        <v>9.805199999999999</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>259.5389</v>
+        <v>259.476</v>
       </c>
       <c r="D76" s="2" t="n">
         <v>0.0183</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>0.12</v>
+        <v>0.1199</v>
       </c>
     </row>
     <row r="77">
@@ -1753,16 +1753,16 @@
         <v>550</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>9.0237</v>
+        <v>9.0281</v>
       </c>
       <c r="C77" s="2" t="n">
-        <v>272.3934</v>
+        <v>272.3151</v>
       </c>
       <c r="D77" s="2" t="n">
         <v>0.0182</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>0.1289</v>
+        <v>0.1288</v>
       </c>
     </row>
     <row r="78">
@@ -1770,16 +1770,16 @@
         <v>552</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>8.2629</v>
+        <v>8.266999999999999</v>
       </c>
       <c r="C78" s="2" t="n">
-        <v>287.9518</v>
+        <v>287.8611</v>
       </c>
       <c r="D78" s="2" t="n">
         <v>0.0181</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>0.1398</v>
+        <v>0.1397</v>
       </c>
     </row>
     <row r="79">
@@ -1787,10 +1787,10 @@
         <v>554</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>7.5417</v>
+        <v>7.5444</v>
       </c>
       <c r="C79" s="2" t="n">
-        <v>308.0282</v>
+        <v>307.9375</v>
       </c>
       <c r="D79" s="2" t="n">
         <v>0.0179</v>
@@ -1804,10 +1804,10 @@
         <v>556</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>7.0246</v>
+        <v>7.0255</v>
       </c>
       <c r="C80" s="2" t="n">
-        <v>331.6715</v>
+        <v>331.6072</v>
       </c>
       <c r="D80" s="2" t="n">
         <v>0.0178</v>
@@ -1824,7 +1824,7 @@
         <v>6.8705</v>
       </c>
       <c r="C81" s="2" t="n">
-        <v>358.4253</v>
+        <v>358.4136</v>
       </c>
       <c r="D81" s="2" t="n">
         <v>0.0177</v>
@@ -1838,10 +1838,10 @@
         <v>560</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>7.1919</v>
+        <v>7.1927</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>24.5405</v>
+        <v>24.5818</v>
       </c>
       <c r="D82" s="2" t="n">
         <v>0.0176</v>
@@ -1855,16 +1855,16 @@
         <v>562</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>7.8565</v>
+        <v>7.859</v>
       </c>
       <c r="C83" s="2" t="n">
-        <v>47.193</v>
+        <v>47.2632</v>
       </c>
       <c r="D83" s="2" t="n">
         <v>0.0175</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>0.1419</v>
+        <v>0.1418</v>
       </c>
     </row>
     <row r="84">
@@ -1872,10 +1872,10 @@
         <v>564</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>8.630100000000001</v>
+        <v>8.633599999999999</v>
       </c>
       <c r="C84" s="2" t="n">
-        <v>65.4598</v>
+        <v>65.53530000000001</v>
       </c>
       <c r="D84" s="2" t="n">
         <v>0.0174</v>
@@ -1889,10 +1889,10 @@
         <v>566</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>9.3888</v>
+        <v>9.3926</v>
       </c>
       <c r="C85" s="2" t="n">
-        <v>80.73520000000001</v>
+        <v>80.8027</v>
       </c>
       <c r="D85" s="2" t="n">
         <v>0.0173</v>
@@ -1906,10 +1906,10 @@
         <v>568</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>10.1328</v>
+        <v>10.1363</v>
       </c>
       <c r="C86" s="2" t="n">
-        <v>92.51609999999999</v>
+        <v>92.57170000000001</v>
       </c>
       <c r="D86" s="2" t="n">
         <v>0.0172</v>
@@ -1923,10 +1923,10 @@
         <v>570</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>10.7378</v>
+        <v>10.7407</v>
       </c>
       <c r="C87" s="2" t="n">
-        <v>102.4126</v>
+        <v>102.4567</v>
       </c>
       <c r="D87" s="2" t="n">
         <v>0.017</v>
@@ -1940,10 +1940,10 @@
         <v>572</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>11.3072</v>
+        <v>11.3096</v>
       </c>
       <c r="C88" s="2" t="n">
-        <v>110.5682</v>
+        <v>110.6026</v>
       </c>
       <c r="D88" s="2" t="n">
         <v>0.0169</v>
@@ -1957,10 +1957,10 @@
         <v>574</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>11.8056</v>
+        <v>11.8076</v>
       </c>
       <c r="C89" s="2" t="n">
-        <v>117.65</v>
+        <v>117.6768</v>
       </c>
       <c r="D89" s="2" t="n">
         <v>0.0168</v>
@@ -1974,10 +1974,10 @@
         <v>576</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>12.2715</v>
+        <v>12.273</v>
       </c>
       <c r="C90" s="2" t="n">
-        <v>123.8748</v>
+        <v>123.8958</v>
       </c>
       <c r="D90" s="2" t="n">
         <v>0.0168</v>
@@ -1991,10 +1991,10 @@
         <v>578</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>12.6735</v>
+        <v>12.6748</v>
       </c>
       <c r="C91" s="2" t="n">
-        <v>129.1906</v>
+        <v>129.2072</v>
       </c>
       <c r="D91" s="2" t="n">
         <v>0.0167</v>
@@ -2008,10 +2008,10 @@
         <v>580</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>13.0488</v>
+        <v>13.0498</v>
       </c>
       <c r="C92" s="2" t="n">
-        <v>134.1289</v>
+        <v>134.1421</v>
       </c>
       <c r="D92" s="2" t="n">
         <v>0.0166</v>
@@ -2025,10 +2025,10 @@
         <v>582</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>13.3797</v>
+        <v>13.3805</v>
       </c>
       <c r="C93" s="2" t="n">
-        <v>138.82</v>
+        <v>138.8306</v>
       </c>
       <c r="D93" s="2" t="n">
         <v>0.0165</v>
@@ -2042,16 +2042,16 @@
         <v>584</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>13.6781</v>
+        <v>13.6787</v>
       </c>
       <c r="C94" s="2" t="n">
-        <v>142.8788</v>
+        <v>142.8874</v>
       </c>
       <c r="D94" s="2" t="n">
         <v>0.0164</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>0.0786</v>
+        <v>0.0785</v>
       </c>
     </row>
     <row r="95">
@@ -2059,10 +2059,10 @@
         <v>586</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>13.9182</v>
+        <v>13.9186</v>
       </c>
       <c r="C95" s="2" t="n">
-        <v>146.8792</v>
+        <v>146.8861</v>
       </c>
       <c r="D95" s="2" t="n">
         <v>0.0163</v>
@@ -2076,10 +2076,10 @@
         <v>588</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>14.1795</v>
+        <v>14.1798</v>
       </c>
       <c r="C96" s="2" t="n">
-        <v>150.7935</v>
+        <v>150.7992</v>
       </c>
       <c r="D96" s="2" t="n">
         <v>0.0162</v>
@@ -2093,10 +2093,10 @@
         <v>590</v>
       </c>
       <c r="B97" s="2" t="n">
-        <v>14.3237</v>
+        <v>14.3239</v>
       </c>
       <c r="C97" s="2" t="n">
-        <v>154.4647</v>
+        <v>154.4693</v>
       </c>
       <c r="D97" s="2" t="n">
         <v>0.0162</v>
@@ -2110,10 +2110,10 @@
         <v>592</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>14.5125</v>
+        <v>14.5127</v>
       </c>
       <c r="C98" s="2" t="n">
-        <v>158.237</v>
+        <v>158.2406</v>
       </c>
       <c r="D98" s="2" t="n">
         <v>0.0161</v>
@@ -2127,10 +2127,10 @@
         <v>594</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>14.663</v>
+        <v>14.6631</v>
       </c>
       <c r="C99" s="2" t="n">
-        <v>161.4587</v>
+        <v>161.4615</v>
       </c>
       <c r="D99" s="2" t="n">
         <v>0.016</v>
@@ -2144,10 +2144,10 @@
         <v>596</v>
       </c>
       <c r="B100" s="2" t="n">
-        <v>14.7734</v>
+        <v>14.7735</v>
       </c>
       <c r="C100" s="2" t="n">
-        <v>164.8896</v>
+        <v>164.8918</v>
       </c>
       <c r="D100" s="2" t="n">
         <v>0.0159</v>
@@ -2164,7 +2164,7 @@
         <v>14.8343</v>
       </c>
       <c r="C101" s="2" t="n">
-        <v>168.288</v>
+        <v>168.2896</v>
       </c>
       <c r="D101" s="2" t="n">
         <v>0.0159</v>
@@ -2181,7 +2181,7 @@
         <v>14.894</v>
       </c>
       <c r="C102" s="2" t="n">
-        <v>171.4965</v>
+        <v>171.4975</v>
       </c>
       <c r="D102" s="2" t="n">
         <v>0.0158</v>
@@ -2198,7 +2198,7 @@
         <v>14.9023</v>
       </c>
       <c r="C103" s="2" t="n">
-        <v>174.7913</v>
+        <v>174.7918</v>
       </c>
       <c r="D103" s="2" t="n">
         <v>0.0157</v>
@@ -2232,7 +2232,7 @@
         <v>14.8428</v>
       </c>
       <c r="C105" s="2" t="n">
-        <v>181.1904</v>
+        <v>181.1899</v>
       </c>
       <c r="D105" s="2" t="n">
         <v>0.0156</v>
@@ -2246,10 +2246,10 @@
         <v>608</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>14.8251</v>
+        <v>14.8252</v>
       </c>
       <c r="C106" s="2" t="n">
-        <v>184.4433</v>
+        <v>184.4424</v>
       </c>
       <c r="D106" s="2" t="n">
         <v>0.0156</v>
@@ -2263,10 +2263,10 @@
         <v>610</v>
       </c>
       <c r="B107" s="2" t="n">
-        <v>14.6938</v>
+        <v>14.6939</v>
       </c>
       <c r="C107" s="2" t="n">
-        <v>187.6331</v>
+        <v>187.6317</v>
       </c>
       <c r="D107" s="2" t="n">
         <v>0.0155</v>
@@ -2280,10 +2280,10 @@
         <v>612</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>14.5743</v>
+        <v>14.5744</v>
       </c>
       <c r="C108" s="2" t="n">
-        <v>190.8398</v>
+        <v>190.8379</v>
       </c>
       <c r="D108" s="2" t="n">
         <v>0.0155</v>
@@ -2297,10 +2297,10 @@
         <v>614</v>
       </c>
       <c r="B109" s="2" t="n">
-        <v>14.4431</v>
+        <v>14.4433</v>
       </c>
       <c r="C109" s="2" t="n">
-        <v>194.0233</v>
+        <v>194.0209</v>
       </c>
       <c r="D109" s="2" t="n">
         <v>0.0154</v>
@@ -2314,10 +2314,10 @@
         <v>616</v>
       </c>
       <c r="B110" s="2" t="n">
-        <v>14.2784</v>
+        <v>14.2786</v>
       </c>
       <c r="C110" s="2" t="n">
-        <v>197.2568</v>
+        <v>197.2539</v>
       </c>
       <c r="D110" s="2" t="n">
         <v>0.0154</v>
@@ -2331,10 +2331,10 @@
         <v>618</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>14.0785</v>
+        <v>14.0787</v>
       </c>
       <c r="C111" s="2" t="n">
-        <v>200.3701</v>
+        <v>200.3666</v>
       </c>
       <c r="D111" s="2" t="n">
         <v>0.0153</v>
@@ -2348,10 +2348,10 @@
         <v>620</v>
       </c>
       <c r="B112" s="2" t="n">
-        <v>13.8363</v>
+        <v>13.8366</v>
       </c>
       <c r="C112" s="2" t="n">
-        <v>203.9387</v>
+        <v>203.9346</v>
       </c>
       <c r="D112" s="2" t="n">
         <v>0.0153</v>
@@ -2365,10 +2365,10 @@
         <v>622</v>
       </c>
       <c r="B113" s="2" t="n">
-        <v>13.6274</v>
+        <v>13.6278</v>
       </c>
       <c r="C113" s="2" t="n">
-        <v>207.3468</v>
+        <v>207.342</v>
       </c>
       <c r="D113" s="2" t="n">
         <v>0.0153</v>
@@ -2382,10 +2382,10 @@
         <v>624</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>13.3724</v>
+        <v>13.3728</v>
       </c>
       <c r="C114" s="2" t="n">
-        <v>210.7938</v>
+        <v>210.7882</v>
       </c>
       <c r="D114" s="2" t="n">
         <v>0.0152</v>
@@ -2399,10 +2399,10 @@
         <v>626</v>
       </c>
       <c r="B115" s="2" t="n">
-        <v>13.1129</v>
+        <v>13.1134</v>
       </c>
       <c r="C115" s="2" t="n">
-        <v>214.1346</v>
+        <v>214.1281</v>
       </c>
       <c r="D115" s="2" t="n">
         <v>0.0152</v>
@@ -2416,10 +2416,10 @@
         <v>628</v>
       </c>
       <c r="B116" s="2" t="n">
-        <v>12.8174</v>
+        <v>12.818</v>
       </c>
       <c r="C116" s="2" t="n">
-        <v>218.0455</v>
+        <v>218.0379</v>
       </c>
       <c r="D116" s="2" t="n">
         <v>0.0152</v>
@@ -2433,10 +2433,10 @@
         <v>630</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>12.4969</v>
+        <v>12.4976</v>
       </c>
       <c r="C117" s="2" t="n">
-        <v>221.7829</v>
+        <v>221.774</v>
       </c>
       <c r="D117" s="2" t="n">
         <v>0.0151</v>
@@ -2450,10 +2450,10 @@
         <v>632</v>
       </c>
       <c r="B118" s="2" t="n">
-        <v>12.164</v>
+        <v>12.1648</v>
       </c>
       <c r="C118" s="2" t="n">
-        <v>225.8298</v>
+        <v>225.8194</v>
       </c>
       <c r="D118" s="2" t="n">
         <v>0.0151</v>
@@ -2467,10 +2467,10 @@
         <v>634</v>
       </c>
       <c r="B119" s="2" t="n">
-        <v>11.8095</v>
+        <v>11.8105</v>
       </c>
       <c r="C119" s="2" t="n">
-        <v>230.2347</v>
+        <v>230.2225</v>
       </c>
       <c r="D119" s="2" t="n">
         <v>0.0151</v>
@@ -2484,10 +2484,10 @@
         <v>636</v>
       </c>
       <c r="B120" s="2" t="n">
-        <v>11.4556</v>
+        <v>11.4567</v>
       </c>
       <c r="C120" s="2" t="n">
-        <v>234.9554</v>
+        <v>234.941</v>
       </c>
       <c r="D120" s="2" t="n">
         <v>0.0151</v>
@@ -2501,10 +2501,10 @@
         <v>638</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>11.0565</v>
+        <v>11.0578</v>
       </c>
       <c r="C121" s="2" t="n">
-        <v>240.1317</v>
+        <v>240.1146</v>
       </c>
       <c r="D121" s="2" t="n">
         <v>0.015</v>
@@ -2518,16 +2518,16 @@
         <v>640</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>10.6716</v>
+        <v>10.6731</v>
       </c>
       <c r="C122" s="2" t="n">
-        <v>245.7942</v>
+        <v>245.774</v>
       </c>
       <c r="D122" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>0.091</v>
+        <v>0.09089999999999999</v>
       </c>
     </row>
     <row r="123">
@@ -2535,10 +2535,10 @@
         <v>642</v>
       </c>
       <c r="B123" s="2" t="n">
-        <v>10.2123</v>
+        <v>10.2139</v>
       </c>
       <c r="C123" s="2" t="n">
-        <v>251.9425</v>
+        <v>251.9186</v>
       </c>
       <c r="D123" s="2" t="n">
         <v>0.015</v>
@@ -2552,16 +2552,16 @@
         <v>644</v>
       </c>
       <c r="B124" s="2" t="n">
-        <v>9.7582</v>
+        <v>9.76</v>
       </c>
       <c r="C124" s="2" t="n">
-        <v>259.1186</v>
+        <v>259.0904</v>
       </c>
       <c r="D124" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>0.0987</v>
+        <v>0.09859999999999999</v>
       </c>
     </row>
     <row r="125">
@@ -2569,10 +2569,10 @@
         <v>646</v>
       </c>
       <c r="B125" s="2" t="n">
-        <v>9.303000000000001</v>
+        <v>9.3049</v>
       </c>
       <c r="C125" s="2" t="n">
-        <v>267.3754</v>
+        <v>267.3427</v>
       </c>
       <c r="D125" s="2" t="n">
         <v>0.015</v>
@@ -2586,10 +2586,10 @@
         <v>648</v>
       </c>
       <c r="B126" s="2" t="n">
-        <v>8.8078</v>
+        <v>8.8096</v>
       </c>
       <c r="C126" s="2" t="n">
-        <v>276.4297</v>
+        <v>276.3926</v>
       </c>
       <c r="D126" s="2" t="n">
         <v>0.015</v>
@@ -2603,10 +2603,10 @@
         <v>650</v>
       </c>
       <c r="B127" s="2" t="n">
-        <v>8.3169</v>
+        <v>8.3186</v>
       </c>
       <c r="C127" s="2" t="n">
-        <v>287.1692</v>
+        <v>287.1287</v>
       </c>
       <c r="D127" s="2" t="n">
         <v>0.015</v>
@@ -2620,16 +2620,16 @@
         <v>652</v>
       </c>
       <c r="B128" s="2" t="n">
-        <v>7.8716</v>
+        <v>7.873</v>
       </c>
       <c r="C128" s="2" t="n">
-        <v>299.3926</v>
+        <v>299.351</v>
       </c>
       <c r="D128" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>0.1218</v>
+        <v>0.1217</v>
       </c>
     </row>
     <row r="129">
@@ -2637,10 +2637,10 @@
         <v>654</v>
       </c>
       <c r="B129" s="2" t="n">
-        <v>7.4497</v>
+        <v>7.4506</v>
       </c>
       <c r="C129" s="2" t="n">
-        <v>313.8424</v>
+        <v>313.8039</v>
       </c>
       <c r="D129" s="2" t="n">
         <v>0.015</v>
@@ -2654,10 +2654,10 @@
         <v>656</v>
       </c>
       <c r="B130" s="2" t="n">
-        <v>7.1548</v>
+        <v>7.1552</v>
       </c>
       <c r="C130" s="2" t="n">
-        <v>329.5268</v>
+        <v>329.4969</v>
       </c>
       <c r="D130" s="2" t="n">
         <v>0.015</v>
@@ -2671,10 +2671,10 @@
         <v>658</v>
       </c>
       <c r="B131" s="2" t="n">
-        <v>7.0224</v>
+        <v>7.0225</v>
       </c>
       <c r="C131" s="2" t="n">
-        <v>346.964</v>
+        <v>346.9484</v>
       </c>
       <c r="D131" s="2" t="n">
         <v>0.015</v>
@@ -2691,7 +2691,7 @@
         <v>7.0348</v>
       </c>
       <c r="C132" s="2" t="n">
-        <v>4.2883</v>
+        <v>4.2897</v>
       </c>
       <c r="D132" s="2" t="n">
         <v>0.015</v>
@@ -2705,10 +2705,10 @@
         <v>662</v>
       </c>
       <c r="B133" s="2" t="n">
-        <v>7.2098</v>
+        <v>7.2101</v>
       </c>
       <c r="C133" s="2" t="n">
-        <v>21.4475</v>
+        <v>21.4642</v>
       </c>
       <c r="D133" s="2" t="n">
         <v>0.015</v>
@@ -2722,10 +2722,10 @@
         <v>664</v>
       </c>
       <c r="B134" s="2" t="n">
-        <v>7.5758</v>
+        <v>7.5765</v>
       </c>
       <c r="C134" s="2" t="n">
-        <v>37.1983</v>
+        <v>37.2258</v>
       </c>
       <c r="D134" s="2" t="n">
         <v>0.015</v>
@@ -2739,10 +2739,10 @@
         <v>666</v>
       </c>
       <c r="B135" s="2" t="n">
-        <v>8.0236</v>
+        <v>8.024800000000001</v>
       </c>
       <c r="C135" s="2" t="n">
-        <v>51.2125</v>
+        <v>51.2453</v>
       </c>
       <c r="D135" s="2" t="n">
         <v>0.015</v>
@@ -2756,10 +2756,10 @@
         <v>668</v>
       </c>
       <c r="B136" s="2" t="n">
-        <v>8.4764</v>
+        <v>8.4779</v>
       </c>
       <c r="C136" s="2" t="n">
-        <v>63.2384</v>
+        <v>63.2724</v>
       </c>
       <c r="D136" s="2" t="n">
         <v>0.015</v>
@@ -2773,10 +2773,10 @@
         <v>670</v>
       </c>
       <c r="B137" s="2" t="n">
-        <v>8.942</v>
+        <v>8.9436</v>
       </c>
       <c r="C137" s="2" t="n">
-        <v>73.9267</v>
+        <v>73.9588</v>
       </c>
       <c r="D137" s="2" t="n">
         <v>0.015</v>
@@ -2790,16 +2790,16 @@
         <v>672</v>
       </c>
       <c r="B138" s="2" t="n">
-        <v>9.408200000000001</v>
+        <v>9.409800000000001</v>
       </c>
       <c r="C138" s="2" t="n">
-        <v>83.1956</v>
+        <v>83.2247</v>
       </c>
       <c r="D138" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>0.1022</v>
+        <v>0.1021</v>
       </c>
     </row>
     <row r="139">
@@ -2807,10 +2807,10 @@
         <v>674</v>
       </c>
       <c r="B139" s="2" t="n">
-        <v>9.8385</v>
+        <v>9.8399</v>
       </c>
       <c r="C139" s="2" t="n">
-        <v>91.02809999999999</v>
+        <v>91.0536</v>
       </c>
       <c r="D139" s="2" t="n">
         <v>0.015</v>
@@ -2824,10 +2824,10 @@
         <v>676</v>
       </c>
       <c r="B140" s="2" t="n">
-        <v>10.2789</v>
+        <v>10.2802</v>
       </c>
       <c r="C140" s="2" t="n">
-        <v>98.0283</v>
+        <v>98.0502</v>
       </c>
       <c r="D140" s="2" t="n">
         <v>0.015</v>
@@ -2841,16 +2841,16 @@
         <v>678</v>
       </c>
       <c r="B141" s="2" t="n">
-        <v>10.6397</v>
+        <v>10.6409</v>
       </c>
       <c r="C141" s="2" t="n">
-        <v>104.2526</v>
+        <v>104.2712</v>
       </c>
       <c r="D141" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>0.091</v>
+        <v>0.09089999999999999</v>
       </c>
     </row>
     <row r="142">
@@ -2858,10 +2858,10 @@
         <v>680</v>
       </c>
       <c r="B142" s="2" t="n">
-        <v>10.9832</v>
+        <v>10.9842</v>
       </c>
       <c r="C142" s="2" t="n">
-        <v>109.7262</v>
+        <v>109.742</v>
       </c>
       <c r="D142" s="2" t="n">
         <v>0.015</v>
@@ -2875,10 +2875,10 @@
         <v>682</v>
       </c>
       <c r="B143" s="2" t="n">
-        <v>11.3053</v>
+        <v>11.3061</v>
       </c>
       <c r="C143" s="2" t="n">
-        <v>114.5296</v>
+        <v>114.5429</v>
       </c>
       <c r="D143" s="2" t="n">
         <v>0.015</v>
@@ -2892,10 +2892,10 @@
         <v>684</v>
       </c>
       <c r="B144" s="2" t="n">
-        <v>11.594</v>
+        <v>11.5948</v>
       </c>
       <c r="C144" s="2" t="n">
-        <v>119.2112</v>
+        <v>119.2225</v>
       </c>
       <c r="D144" s="2" t="n">
         <v>0.015</v>
@@ -2909,10 +2909,10 @@
         <v>686</v>
       </c>
       <c r="B145" s="2" t="n">
-        <v>11.877</v>
+        <v>11.8777</v>
       </c>
       <c r="C145" s="2" t="n">
-        <v>123.2071</v>
+        <v>123.2167</v>
       </c>
       <c r="D145" s="2" t="n">
         <v>0.015</v>
@@ -2926,10 +2926,10 @@
         <v>688</v>
       </c>
       <c r="B146" s="2" t="n">
-        <v>12.1345</v>
+        <v>12.1351</v>
       </c>
       <c r="C146" s="2" t="n">
-        <v>127.0964</v>
+        <v>127.1045</v>
       </c>
       <c r="D146" s="2" t="n">
         <v>0.015</v>
@@ -2943,10 +2943,10 @@
         <v>690</v>
       </c>
       <c r="B147" s="2" t="n">
-        <v>12.3783</v>
+        <v>12.3788</v>
       </c>
       <c r="C147" s="2" t="n">
-        <v>130.614</v>
+        <v>130.621</v>
       </c>
       <c r="D147" s="2" t="n">
         <v>0.015</v>
@@ -2960,10 +2960,10 @@
         <v>692</v>
       </c>
       <c r="B148" s="2" t="n">
-        <v>12.6195</v>
+        <v>12.6199</v>
       </c>
       <c r="C148" s="2" t="n">
-        <v>133.7535</v>
+        <v>133.7595</v>
       </c>
       <c r="D148" s="2" t="n">
         <v>0.015</v>
@@ -2977,10 +2977,10 @@
         <v>694</v>
       </c>
       <c r="B149" s="2" t="n">
-        <v>12.826</v>
+        <v>12.8263</v>
       </c>
       <c r="C149" s="2" t="n">
-        <v>137.0084</v>
+        <v>137.0135</v>
       </c>
       <c r="D149" s="2" t="n">
         <v>0.015</v>
@@ -2994,10 +2994,10 @@
         <v>696</v>
       </c>
       <c r="B150" s="2" t="n">
-        <v>13.0229</v>
+        <v>13.0232</v>
       </c>
       <c r="C150" s="2" t="n">
-        <v>139.9828</v>
+        <v>139.9873</v>
       </c>
       <c r="D150" s="2" t="n">
         <v>0.015</v>
@@ -3011,10 +3011,10 @@
         <v>698</v>
       </c>
       <c r="B151" s="2" t="n">
-        <v>13.2189</v>
+        <v>13.2192</v>
       </c>
       <c r="C151" s="2" t="n">
-        <v>142.9093</v>
+        <v>142.9131</v>
       </c>
       <c r="D151" s="2" t="n">
         <v>0.015</v>
@@ -3028,10 +3028,10 @@
         <v>700</v>
       </c>
       <c r="B152" s="2" t="n">
-        <v>13.3912</v>
+        <v>13.3914</v>
       </c>
       <c r="C152" s="2" t="n">
-        <v>145.658</v>
+        <v>145.6613</v>
       </c>
       <c r="D152" s="2" t="n">
         <v>0.015</v>
@@ -3045,10 +3045,10 @@
         <v>702</v>
       </c>
       <c r="B153" s="2" t="n">
-        <v>13.5477</v>
+        <v>13.5479</v>
       </c>
       <c r="C153" s="2" t="n">
-        <v>148.4152</v>
+        <v>148.4182</v>
       </c>
       <c r="D153" s="2" t="n">
         <v>0.015</v>
@@ -3062,10 +3062,10 @@
         <v>704</v>
       </c>
       <c r="B154" s="2" t="n">
-        <v>13.6661</v>
+        <v>13.6662</v>
       </c>
       <c r="C154" s="2" t="n">
-        <v>150.9197</v>
+        <v>150.9222</v>
       </c>
       <c r="D154" s="2" t="n">
         <v>0.015</v>
@@ -3079,10 +3079,10 @@
         <v>706</v>
       </c>
       <c r="B155" s="2" t="n">
-        <v>13.804</v>
+        <v>13.8042</v>
       </c>
       <c r="C155" s="2" t="n">
-        <v>153.4455</v>
+        <v>153.4477</v>
       </c>
       <c r="D155" s="2" t="n">
         <v>0.015</v>
@@ -3096,10 +3096,10 @@
         <v>708</v>
       </c>
       <c r="B156" s="2" t="n">
-        <v>13.9051</v>
+        <v>13.9052</v>
       </c>
       <c r="C156" s="2" t="n">
-        <v>155.8236</v>
+        <v>155.8255</v>
       </c>
       <c r="D156" s="2" t="n">
         <v>0.015</v>
@@ -3116,7 +3116,7 @@
         <v>14.0313</v>
       </c>
       <c r="C157" s="2" t="n">
-        <v>158.2027</v>
+        <v>158.2043</v>
       </c>
       <c r="D157" s="2" t="n">
         <v>0.015</v>
@@ -3133,7 +3133,7 @@
         <v>14.135</v>
       </c>
       <c r="C158" s="2" t="n">
-        <v>160.6647</v>
+        <v>160.6661</v>
       </c>
       <c r="D158" s="2" t="n">
         <v>0.015</v>
@@ -3150,7 +3150,7 @@
         <v>14.2049</v>
       </c>
       <c r="C159" s="2" t="n">
-        <v>162.9174</v>
+        <v>162.9185</v>
       </c>
       <c r="D159" s="2" t="n">
         <v>0.015</v>
@@ -3167,7 +3167,7 @@
         <v>14.2609</v>
       </c>
       <c r="C160" s="2" t="n">
-        <v>165.1857</v>
+        <v>165.1867</v>
       </c>
       <c r="D160" s="2" t="n">
         <v>0.015</v>
@@ -3184,7 +3184,7 @@
         <v>14.3521</v>
       </c>
       <c r="C161" s="2" t="n">
-        <v>167.5089</v>
+        <v>167.5096</v>
       </c>
       <c r="D161" s="2" t="n">
         <v>0.015</v>
@@ -3201,7 +3201,7 @@
         <v>14.3622</v>
       </c>
       <c r="C162" s="2" t="n">
-        <v>169.6253</v>
+        <v>169.6259</v>
       </c>
       <c r="D162" s="2" t="n">
         <v>0.015</v>
@@ -3218,7 +3218,7 @@
         <v>14.4003</v>
       </c>
       <c r="C163" s="2" t="n">
-        <v>171.8993</v>
+        <v>171.8997</v>
       </c>
       <c r="D163" s="2" t="n">
         <v>0.015</v>
@@ -3235,7 +3235,7 @@
         <v>14.3939</v>
       </c>
       <c r="C164" s="2" t="n">
-        <v>174.1624</v>
+        <v>174.1627</v>
       </c>
       <c r="D164" s="2" t="n">
         <v>0.015</v>
@@ -3252,7 +3252,7 @@
         <v>14.4129</v>
       </c>
       <c r="C165" s="2" t="n">
-        <v>176.2818</v>
+        <v>176.282</v>
       </c>
       <c r="D165" s="2" t="n">
         <v>0.015</v>
@@ -3286,7 +3286,7 @@
         <v>14.382</v>
       </c>
       <c r="C167" s="2" t="n">
-        <v>180.649</v>
+        <v>180.6489</v>
       </c>
       <c r="D167" s="2" t="n">
         <v>0.015</v>
@@ -3303,7 +3303,7 @@
         <v>14.3389</v>
       </c>
       <c r="C168" s="2" t="n">
-        <v>182.7282</v>
+        <v>182.7279</v>
       </c>
       <c r="D168" s="2" t="n">
         <v>0.015</v>
@@ -3317,10 +3317,10 @@
         <v>734</v>
       </c>
       <c r="B169" s="2" t="n">
-        <v>14.3058</v>
+        <v>14.3059</v>
       </c>
       <c r="C169" s="2" t="n">
-        <v>184.9356</v>
+        <v>184.9352</v>
       </c>
       <c r="D169" s="2" t="n">
         <v>0.015</v>
@@ -3334,10 +3334,10 @@
         <v>736</v>
       </c>
       <c r="B170" s="2" t="n">
-        <v>14.2422</v>
+        <v>14.2423</v>
       </c>
       <c r="C170" s="2" t="n">
-        <v>187.0266</v>
+        <v>187.0261</v>
       </c>
       <c r="D170" s="2" t="n">
         <v>0.015</v>
@@ -3354,7 +3354,7 @@
         <v>14.1783</v>
       </c>
       <c r="C171" s="2" t="n">
-        <v>189.137</v>
+        <v>189.1363</v>
       </c>
       <c r="D171" s="2" t="n">
         <v>0.015</v>
@@ -3371,7 +3371,7 @@
         <v>14.1065</v>
       </c>
       <c r="C172" s="2" t="n">
-        <v>191.2614</v>
+        <v>191.2605</v>
       </c>
       <c r="D172" s="2" t="n">
         <v>0.015</v>
@@ -3388,7 +3388,7 @@
         <v>14.0258</v>
       </c>
       <c r="C173" s="2" t="n">
-        <v>193.4435</v>
+        <v>193.4426</v>
       </c>
       <c r="D173" s="2" t="n">
         <v>0.015</v>
@@ -3405,7 +3405,7 @@
         <v>13.8948</v>
       </c>
       <c r="C174" s="2" t="n">
-        <v>195.6098</v>
+        <v>195.6087</v>
       </c>
       <c r="D174" s="2" t="n">
         <v>0.015</v>
@@ -3419,10 +3419,10 @@
         <v>746</v>
       </c>
       <c r="B175" s="2" t="n">
-        <v>13.8166</v>
+        <v>13.8167</v>
       </c>
       <c r="C175" s="2" t="n">
-        <v>197.5826</v>
+        <v>197.5814</v>
       </c>
       <c r="D175" s="2" t="n">
         <v>0.015</v>
@@ -3436,10 +3436,10 @@
         <v>748</v>
       </c>
       <c r="B176" s="2" t="n">
-        <v>13.7139</v>
+        <v>13.714</v>
       </c>
       <c r="C176" s="2" t="n">
-        <v>199.9144</v>
+        <v>199.913</v>
       </c>
       <c r="D176" s="2" t="n">
         <v>0.015</v>
@@ -3453,10 +3453,10 @@
         <v>750</v>
       </c>
       <c r="B177" s="2" t="n">
-        <v>13.6176</v>
+        <v>13.6177</v>
       </c>
       <c r="C177" s="2" t="n">
-        <v>202.0928</v>
+        <v>202.0912</v>
       </c>
       <c r="D177" s="2" t="n">
         <v>0.015</v>
@@ -3470,10 +3470,10 @@
         <v>752</v>
       </c>
       <c r="B178" s="2" t="n">
-        <v>13.4801</v>
+        <v>13.4802</v>
       </c>
       <c r="C178" s="2" t="n">
-        <v>204.2227</v>
+        <v>204.221</v>
       </c>
       <c r="D178" s="2" t="n">
         <v>0.015</v>
@@ -3487,10 +3487,10 @@
         <v>754</v>
       </c>
       <c r="B179" s="2" t="n">
-        <v>13.3113</v>
+        <v>13.3114</v>
       </c>
       <c r="C179" s="2" t="n">
-        <v>206.4521</v>
+        <v>206.4501</v>
       </c>
       <c r="D179" s="2" t="n">
         <v>0.015</v>
@@ -3504,10 +3504,10 @@
         <v>756</v>
       </c>
       <c r="B180" s="2" t="n">
-        <v>13.188</v>
+        <v>13.1882</v>
       </c>
       <c r="C180" s="2" t="n">
-        <v>208.8821</v>
+        <v>208.8799</v>
       </c>
       <c r="D180" s="2" t="n">
         <v>0.015</v>
@@ -3521,10 +3521,10 @@
         <v>758</v>
       </c>
       <c r="B181" s="2" t="n">
-        <v>13.0168</v>
+        <v>13.0169</v>
       </c>
       <c r="C181" s="2" t="n">
-        <v>211.0154</v>
+        <v>211.013</v>
       </c>
       <c r="D181" s="2" t="n">
         <v>0.015</v>
@@ -3538,10 +3538,10 @@
         <v>760</v>
       </c>
       <c r="B182" s="2" t="n">
-        <v>12.8704</v>
+        <v>12.8706</v>
       </c>
       <c r="C182" s="2" t="n">
-        <v>213.2541</v>
+        <v>213.2515</v>
       </c>
       <c r="D182" s="2" t="n">
         <v>0.015</v>
@@ -3555,10 +3555,10 @@
         <v>762</v>
       </c>
       <c r="B183" s="2" t="n">
-        <v>12.6773</v>
+        <v>12.6775</v>
       </c>
       <c r="C183" s="2" t="n">
-        <v>215.6262</v>
+        <v>215.6234</v>
       </c>
       <c r="D183" s="2" t="n">
         <v>0.015</v>
@@ -3572,10 +3572,10 @@
         <v>764</v>
       </c>
       <c r="B184" s="2" t="n">
-        <v>12.4954</v>
+        <v>12.4956</v>
       </c>
       <c r="C184" s="2" t="n">
-        <v>218.1312</v>
+        <v>218.128</v>
       </c>
       <c r="D184" s="2" t="n">
         <v>0.015</v>
@@ -3589,10 +3589,10 @@
         <v>766</v>
       </c>
       <c r="B185" s="2" t="n">
-        <v>12.297</v>
+        <v>12.2972</v>
       </c>
       <c r="C185" s="2" t="n">
-        <v>220.5504</v>
+        <v>220.547</v>
       </c>
       <c r="D185" s="2" t="n">
         <v>0.015</v>
@@ -3606,10 +3606,10 @@
         <v>768</v>
       </c>
       <c r="B186" s="2" t="n">
-        <v>12.1641</v>
+        <v>12.1644</v>
       </c>
       <c r="C186" s="2" t="n">
-        <v>223.2391</v>
+        <v>223.2353</v>
       </c>
       <c r="D186" s="2" t="n">
         <v>0.015</v>
@@ -3623,10 +3623,10 @@
         <v>770</v>
       </c>
       <c r="B187" s="2" t="n">
-        <v>11.9393</v>
+        <v>11.9396</v>
       </c>
       <c r="C187" s="2" t="n">
-        <v>226.0563</v>
+        <v>226.052</v>
       </c>
       <c r="D187" s="2" t="n">
         <v>0.015</v>
@@ -3640,10 +3640,10 @@
         <v>772</v>
       </c>
       <c r="B188" s="2" t="n">
-        <v>11.7038</v>
+        <v>11.7042</v>
       </c>
       <c r="C188" s="2" t="n">
-        <v>228.6427</v>
+        <v>228.638</v>
       </c>
       <c r="D188" s="2" t="n">
         <v>0.015</v>
@@ -3657,10 +3657,10 @@
         <v>774</v>
       </c>
       <c r="B189" s="2" t="n">
-        <v>11.5144</v>
+        <v>11.5148</v>
       </c>
       <c r="C189" s="2" t="n">
-        <v>231.8286</v>
+        <v>231.8234</v>
       </c>
       <c r="D189" s="2" t="n">
         <v>0.015</v>
@@ -3674,10 +3674,10 @@
         <v>776</v>
       </c>
       <c r="B190" s="2" t="n">
-        <v>11.2852</v>
+        <v>11.2856</v>
       </c>
       <c r="C190" s="2" t="n">
-        <v>234.8408</v>
+        <v>234.8351</v>
       </c>
       <c r="D190" s="2" t="n">
         <v>0.015</v>
@@ -3691,10 +3691,10 @@
         <v>778</v>
       </c>
       <c r="B191" s="2" t="n">
-        <v>11.0991</v>
+        <v>11.0995</v>
       </c>
       <c r="C191" s="2" t="n">
-        <v>237.8841</v>
+        <v>237.8778</v>
       </c>
       <c r="D191" s="2" t="n">
         <v>0.015</v>
@@ -3708,10 +3708,10 @@
         <v>780</v>
       </c>
       <c r="B192" s="2" t="n">
-        <v>10.8551</v>
+        <v>10.8555</v>
       </c>
       <c r="C192" s="2" t="n">
-        <v>241.2374</v>
+        <v>241.2303</v>
       </c>
       <c r="D192" s="2" t="n">
         <v>0.015</v>
@@ -3725,10 +3725,10 @@
         <v>782</v>
       </c>
       <c r="B193" s="2" t="n">
-        <v>10.5922</v>
+        <v>10.5927</v>
       </c>
       <c r="C193" s="2" t="n">
-        <v>244.8934</v>
+        <v>244.8856</v>
       </c>
       <c r="D193" s="2" t="n">
         <v>0.015</v>
@@ -3742,10 +3742,10 @@
         <v>784</v>
       </c>
       <c r="B194" s="2" t="n">
-        <v>10.3682</v>
+        <v>10.3687</v>
       </c>
       <c r="C194" s="2" t="n">
-        <v>248.8412</v>
+        <v>248.8325</v>
       </c>
       <c r="D194" s="2" t="n">
         <v>0.015</v>
@@ -3759,16 +3759,16 @@
         <v>786</v>
       </c>
       <c r="B195" s="2" t="n">
-        <v>10.1028</v>
+        <v>10.1034</v>
       </c>
       <c r="C195" s="2" t="n">
-        <v>252.8411</v>
+        <v>252.8315</v>
       </c>
       <c r="D195" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E195" s="2" t="n">
-        <v>0.09569999999999999</v>
+        <v>0.0956</v>
       </c>
     </row>
     <row r="196">
@@ -3776,10 +3776,10 @@
         <v>788</v>
       </c>
       <c r="B196" s="2" t="n">
-        <v>9.834899999999999</v>
+        <v>9.835599999999999</v>
       </c>
       <c r="C196" s="2" t="n">
-        <v>257.0888</v>
+        <v>257.0782</v>
       </c>
       <c r="D196" s="2" t="n">
         <v>0.015</v>
@@ -3793,10 +3793,10 @@
         <v>790</v>
       </c>
       <c r="B197" s="2" t="n">
-        <v>9.5448</v>
+        <v>9.545400000000001</v>
       </c>
       <c r="C197" s="2" t="n">
-        <v>262.0776</v>
+        <v>262.0659</v>
       </c>
       <c r="D197" s="2" t="n">
         <v>0.015</v>
@@ -3810,10 +3810,10 @@
         <v>792</v>
       </c>
       <c r="B198" s="2" t="n">
-        <v>9.285299999999999</v>
+        <v>9.286</v>
       </c>
       <c r="C198" s="2" t="n">
-        <v>267.3709</v>
+        <v>267.358</v>
       </c>
       <c r="D198" s="2" t="n">
         <v>0.015</v>
@@ -3827,10 +3827,10 @@
         <v>794</v>
       </c>
       <c r="B199" s="2" t="n">
-        <v>9.036799999999999</v>
+        <v>9.0375</v>
       </c>
       <c r="C199" s="2" t="n">
-        <v>272.9083</v>
+        <v>272.8944</v>
       </c>
       <c r="D199" s="2" t="n">
         <v>0.015</v>
@@ -3844,10 +3844,10 @@
         <v>796</v>
       </c>
       <c r="B200" s="2" t="n">
-        <v>8.7194</v>
+        <v>8.7201</v>
       </c>
       <c r="C200" s="2" t="n">
-        <v>278.7417</v>
+        <v>278.7268</v>
       </c>
       <c r="D200" s="2" t="n">
         <v>0.015</v>
@@ -3861,10 +3861,10 @@
         <v>798</v>
       </c>
       <c r="B201" s="2" t="n">
-        <v>8.445</v>
+        <v>8.445600000000001</v>
       </c>
       <c r="C201" s="2" t="n">
-        <v>285.5384</v>
+        <v>285.5227</v>
       </c>
       <c r="D201" s="2" t="n">
         <v>0.015</v>
@@ -3878,10 +3878,10 @@
         <v>800</v>
       </c>
       <c r="B202" s="2" t="n">
-        <v>8.1646</v>
+        <v>8.1652</v>
       </c>
       <c r="C202" s="2" t="n">
-        <v>293.069</v>
+        <v>293.0529</v>
       </c>
       <c r="D202" s="2" t="n">
         <v>0.015</v>
